--- a/Output Files GPT-OSS 20B/sensitivity_analysis_gptoss.xlsx
+++ b/Output Files GPT-OSS 20B/sensitivity_analysis_gptoss.xlsx
@@ -413,914 +413,2459 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>scenario_name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>weights_json</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>architecture</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>kendall_tau</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>spearman_rho</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>top1_accuracy</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>top2_accuracy</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>gap_rag_minus_pure</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>gap_param_minus_rag</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>baseline</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>{"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Direct_LLM_Scoring</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>0.053</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>0.059</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>0.3385</v>
       </c>
-      <c r="G2" t="n">
-        <v>1</v>
+      <c r="H2" t="n">
+        <v>0.6513</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.5327999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>baseline</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>{"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>0.3744</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>0.3821</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>0.5641</v>
       </c>
-      <c r="G3" t="n">
-        <v>1</v>
+      <c r="H3" t="n">
+        <v>0.7795</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.5327999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>baseline</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>{"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>0.9072</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>0.9201</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>0.9227</v>
       </c>
-      <c r="G4" t="n">
-        <v>1</v>
+      <c r="H4" t="n">
+        <v>0.9897</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.5327999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>ene +0.05</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>{"energy_cost": 0.35, "environmental": 0.333333, "comfort": 0.183333, "practicality": 0.133333}</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>Direct_LLM_Scoring</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>0.0803</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>0.1</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>0.359</v>
       </c>
-      <c r="G5" t="n">
-        <v>1</v>
+      <c r="H5" t="n">
+        <v>0.6872</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5089000000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>ene +0.05</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>{"energy_cost": 0.35, "environmental": 0.333333, "comfort": 0.183333, "practicality": 0.133333}</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>0.3949</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>0.4077</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>0.5846</v>
       </c>
-      <c r="G6" t="n">
-        <v>1</v>
+      <c r="H6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5089000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>ene +0.05</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>{"energy_cost": 0.35, "environmental": 0.333333, "comfort": 0.183333, "practicality": 0.133333}</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>0.9038</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.9175</v>
       </c>
       <c r="F7" t="n">
         <v>0.9175</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0.9175</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.9845</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5089000000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>ene -0.05</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>{"energy_cost": 0.25, "environmental": 0.366667, "comfort": 0.216667, "practicality": 0.166667}</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Direct_LLM_Scoring</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>0.0735</v>
-      </c>
       <c r="E8" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0803</v>
       </c>
       <c r="F8" t="n">
+        <v>0.0897</v>
+      </c>
+      <c r="G8" t="n">
         <v>0.3641</v>
       </c>
-      <c r="G8" t="n">
-        <v>1</v>
+      <c r="H8" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.2394</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.5978</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>ene -0.05</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>{"energy_cost": 0.25, "environmental": 0.366667, "comfort": 0.216667, "practicality": 0.166667}</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>0.3197</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>0.3359</v>
       </c>
-      <c r="F9" t="n">
-        <v>0.5436</v>
-      </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>0.5385</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.7744</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.2394</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.5978</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>ene -0.05</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>{"energy_cost": 0.25, "environmental": 0.366667, "comfort": 0.216667, "practicality": 0.166667}</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>0.9244</v>
-      </c>
       <c r="E10" t="n">
-        <v>0.9433</v>
+        <v>0.9175</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9381</v>
+        <v>0.9356</v>
       </c>
       <c r="G10" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="H10" t="n">
         <v>1</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.2394</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.5978</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>env +0.05</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>{"energy_cost": 0.283333, "environmental": 0.4, "comfort": 0.183333, "practicality": 0.133333}</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>Direct_LLM_Scoring</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>0.0496</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>0.0615</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>0.3333</v>
       </c>
-      <c r="G11" t="n">
-        <v>1</v>
+      <c r="H11" t="n">
+        <v>0.6564</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5226</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>env +0.05</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>{"energy_cost": 0.283333, "environmental": 0.4, "comfort": 0.183333, "practicality": 0.133333}</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>0.3915</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>0.4051</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>0.5744</v>
       </c>
-      <c r="G12" t="n">
-        <v>1</v>
+      <c r="H12" t="n">
+        <v>0.7846</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.5226</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>env +0.05</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>{"energy_cost": 0.283333, "environmental": 0.4, "comfort": 0.183333, "practicality": 0.133333}</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>0.9141</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.9278</v>
       </c>
       <c r="F13" t="n">
         <v>0.9278</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>0.9278</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.9845</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.5226</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>env -0.05</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>{"energy_cost": 0.316667, "environmental": 0.3, "comfort": 0.216667, "practicality": 0.166667}</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>Direct_LLM_Scoring</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>0.0872</v>
-      </c>
       <c r="E14" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.0906</v>
       </c>
       <c r="F14" t="n">
+        <v>0.0949</v>
+      </c>
+      <c r="G14" t="n">
         <v>0.3641</v>
       </c>
-      <c r="G14" t="n">
-        <v>1</v>
+      <c r="H14" t="n">
+        <v>0.6768999999999999</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.2462</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.591</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>env -0.05</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>{"energy_cost": 0.316667, "environmental": 0.3, "comfort": 0.216667, "practicality": 0.166667}</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>0.3402</v>
-      </c>
       <c r="E15" t="n">
-        <v>0.3513</v>
+        <v>0.3368</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5436</v>
+        <v>0.3487</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>0.5385</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.7795</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.2462</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.591</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>env -0.05</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>{"energy_cost": 0.316667, "environmental": 0.3, "comfort": 0.216667, "practicality": 0.166667}</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>0.9313</v>
-      </c>
       <c r="E16" t="n">
-        <v>0.9485</v>
+        <v>0.9278</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9485</v>
+        <v>0.9459</v>
       </c>
       <c r="G16" t="n">
+        <v>0.9433</v>
+      </c>
+      <c r="H16" t="n">
         <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.2462</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.591</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>com +0.05</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>{"energy_cost": 0.283333, "environmental": 0.333333, "comfort": 0.25, "practicality": 0.133333}</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Direct_LLM_Scoring</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>0.0769</v>
-      </c>
       <c r="E17" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.0803</v>
       </c>
       <c r="F17" t="n">
+        <v>0.0872</v>
+      </c>
+      <c r="G17" t="n">
         <v>0.359</v>
       </c>
-      <c r="G17" t="n">
-        <v>1</v>
+      <c r="H17" t="n">
+        <v>0.6768999999999999</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.5568</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>com +0.05</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>{"energy_cost": 0.283333, "environmental": 0.333333, "comfort": 0.25, "practicality": 0.133333}</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>0.3538</v>
-      </c>
       <c r="E18" t="n">
-        <v>0.3718</v>
+        <v>0.3573</v>
       </c>
       <c r="F18" t="n">
+        <v>0.3744</v>
+      </c>
+      <c r="G18" t="n">
         <v>0.5538</v>
       </c>
-      <c r="G18" t="n">
-        <v>1</v>
+      <c r="H18" t="n">
+        <v>0.7949000000000001</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.5568</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>com +0.05</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>{"energy_cost": 0.283333, "environmental": 0.333333, "comfort": 0.25, "practicality": 0.133333}</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>0.9175</v>
-      </c>
       <c r="E19" t="n">
-        <v>0.9356</v>
+        <v>0.9141</v>
       </c>
       <c r="F19" t="n">
+        <v>0.9304</v>
+      </c>
+      <c r="G19" t="n">
         <v>0.9433</v>
       </c>
-      <c r="G19" t="n">
-        <v>1</v>
+      <c r="H19" t="n">
+        <v>0.9948</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.5568</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>com -0.05</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>{"energy_cost": 0.316667, "environmental": 0.366667, "comfort": 0.15, "practicality": 0.166667}</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Direct_LLM_Scoring</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>0.0974</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>0.1128</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>0.3795</v>
       </c>
-      <c r="G20" t="n">
-        <v>1</v>
+      <c r="H20" t="n">
+        <v>0.6923</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.2838</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.4951</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>com -0.05</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>{"energy_cost": 0.316667, "environmental": 0.366667, "comfort": 0.15, "practicality": 0.166667}</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>0.3812</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>0.3846</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>0.5590000000000001</v>
       </c>
-      <c r="G21" t="n">
-        <v>1</v>
+      <c r="H21" t="n">
+        <v>0.7795</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.2838</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.4951</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>com -0.05</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>{"energy_cost": 0.316667, "environmental": 0.366667, "comfort": 0.15, "practicality": 0.166667}</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>0.8763</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>0.8918</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>0.9021</v>
       </c>
-      <c r="G22" t="n">
-        <v>1</v>
+      <c r="H22" t="n">
+        <v>0.9794</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.2838</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.4951</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>pra +0.05</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>{"energy_cost": 0.283333, "environmental": 0.333333, "comfort": 0.183333, "practicality": 0.2}</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Direct_LLM_Scoring</t>
         </is>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>0.0769</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>0.0795</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>0.3641</v>
       </c>
-      <c r="G23" t="n">
-        <v>1</v>
+      <c r="H23" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.2496</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.5979</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>pra +0.05</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>{"energy_cost": 0.283333, "environmental": 0.333333, "comfort": 0.183333, "practicality": 0.2}</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="D24" t="inlineStr">
         <is>
           <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>0.3265</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>0.3385</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>0.5282</v>
       </c>
-      <c r="G24" t="n">
-        <v>1</v>
+      <c r="H24" t="n">
+        <v>0.7744</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.2496</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.5979</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>pra +0.05</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>{"energy_cost": 0.283333, "environmental": 0.333333, "comfort": 0.183333, "practicality": 0.2}</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>0.9244</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>0.9407</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>0.9485</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.2496</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.5979</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>pra -0.05</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>{"energy_cost": 0.316667, "environmental": 0.366667, "comfort": 0.216667, "practicality": 0.1}</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>Direct_LLM_Scoring</t>
         </is>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>0.0564</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>0.0692</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>0.3436</v>
       </c>
-      <c r="G26" t="n">
-        <v>1</v>
+      <c r="H26" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.5398000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>pra -0.05</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>{"energy_cost": 0.316667, "environmental": 0.366667, "comfort": 0.216667, "practicality": 0.1}</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>0.3915</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>0.4051</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>0.5846</v>
       </c>
-      <c r="G27" t="n">
-        <v>1</v>
+      <c r="H27" t="n">
+        <v>0.7846</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.5398000000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>pra -0.05</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>{"energy_cost": 0.316667, "environmental": 0.366667, "comfort": 0.216667, "practicality": 0.1}</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>0.9313</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>0.9433</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>0.9381</v>
       </c>
-      <c r="G28" t="n">
-        <v>1</v>
+      <c r="H28" t="n">
+        <v>0.9897</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.5398000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>equal</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>{"energy_cost": 0.25, "environmental": 0.25, "comfort": 0.25, "practicality": 0.25}</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Direct_LLM_Scoring</t>
         </is>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>0.1419</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>0.1538</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>0.441</v>
       </c>
-      <c r="G29" t="n">
-        <v>1</v>
+      <c r="H29" t="n">
+        <v>0.7128</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.1949</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.5670000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>equal</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>{"energy_cost": 0.25, "environmental": 0.25, "comfort": 0.25, "practicality": 0.25}</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Example-Guided_LLM_Scoring</t>
         </is>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
         <v>0.3368</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>0.3615</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>0.5538</v>
       </c>
-      <c r="G30" t="n">
-        <v>1</v>
+      <c r="H30" t="n">
+        <v>0.7795</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.1949</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.5670000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>equal</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>{"energy_cost": 0.25, "environmental": 0.25, "comfort": 0.25, "practicality": 0.25}</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>LLM-Parameterized_Reference_Scoring</t>
         </is>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
         <v>0.9038</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>0.9227</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>0.9485</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
+        <v>0.9897</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.1949</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.5670000000000001</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>merec pooled</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>{"energy_cost": 0.19356, "environmental": 0.131075, "comfort": 0.40357, "practicality": 0.271796}</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Direct_LLM_Scoring</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.5231</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.8154</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.04099999999999998</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.5535000000000001</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>merec pooled</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>{"energy_cost": 0.19356, "environmental": 0.131075, "comfort": 0.40357, "practicality": 0.271796}</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Example-Guided_LLM_Scoring</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.4128</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.5949</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.8051</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.04099999999999998</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.5535000000000001</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>merec pooled</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>{"energy_cost": 0.19356, "environmental": 0.131075, "comfort": 0.40357, "practicality": 0.271796}</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>0.9381</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.9536</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.9227</v>
+      </c>
+      <c r="H34" t="n">
         <v>1</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.04099999999999998</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.5535000000000001</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>merec hvac-vec</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>{"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Direct_LLM_Scoring</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.5333</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.2085</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.4101</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>merec hvac-vec</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>{"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Example-Guided_LLM_Scoring</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>0.5521</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.5769</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.8821</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.2085</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.4101</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>merec hvac-vec</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>{"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>0.9622000000000001</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.9716</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.9485</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.2085</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.4101</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>merec appliance-vec</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>{"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Direct_LLM_Scoring</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.4821</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.8256</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.01019999999999999</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.6219000000000001</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>merec appliance-vec</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>{"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Example-Guided_LLM_Scoring</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.5231</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.7846</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.01019999999999999</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.6219000000000001</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>merec appliance-vec</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>{"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>0.9381</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.9536</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.9278</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.01019999999999999</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.6219000000000001</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>merec shower-vec</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>{"energy_cost": 0.248147, "environmental": 0.24439, "comfort": 0.202824, "practicality": 0.304639}</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Direct_LLM_Scoring</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>0.1521</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.1641</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.4462</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.7128</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.1744</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.5704</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>merec shower-vec</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>{"energy_cost": 0.248147, "environmental": 0.24439, "comfort": 0.202824, "practicality": 0.304639}</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Example-Guided_LLM_Scoring</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.5385</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.7846</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.1744</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.5704</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>merec shower-vec</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>{"energy_cost": 0.248147, "environmental": 0.24439, "comfort": 0.202824, "practicality": 0.304639}</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>0.8969</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.9175</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.9897</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.1744</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.5704</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>merec per-type</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.248147, "environmental": 0.24439, "comfort": 0.202824, "practicality": 0.304639}}</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Direct_LLM_Scoring</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>0.2581</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.2744</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.4615</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.7641</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.2017</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.468</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>merec per-type</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.248147, "environmental": 0.24439, "comfort": 0.202824, "practicality": 0.304639}}</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Example-Guided_LLM_Scoring</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>0.4598</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.4821</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.6359</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.2017</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.468</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>merec per-type</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.248147, "environmental": 0.24439, "comfort": 0.202824, "practicality": 0.304639}}</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>0.9278</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.9407</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.9433</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.9897</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.2017</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.468</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>entropy pooled</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>{"energy_cost": 0.268298, "environmental": 0.370515, "comfort": 0.162689, "practicality": 0.198498}</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Direct_LLM_Scoring</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0.0803</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.0897</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.6768999999999999</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.2701</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.5362</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>entropy pooled</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>{"energy_cost": 0.268298, "environmental": 0.370515, "comfort": 0.162689, "practicality": 0.198498}</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Example-Guided_LLM_Scoring</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.5385</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.7846</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.2701</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.5362</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>entropy pooled</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>{"energy_cost": 0.268298, "environmental": 0.370515, "comfort": 0.162689, "practicality": 0.198498}</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0.8866000000000001</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.9046</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.9278</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.9794</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.2701</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.5362</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>entropy hvac-vec</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>{"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Direct_LLM_Scoring</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>0.0701</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.08210000000000001</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.6821</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.5054000000000001</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>entropy hvac-vec</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>{"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Example-Guided_LLM_Scoring</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>0.3949</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.4154</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.5846</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.5054000000000001</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>entropy hvac-vec</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>{"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>0.9003</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.9175</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.9227</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.9897</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.5054000000000001</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>entropy appliance-vec</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>{"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Direct_LLM_Scoring</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>0.0188</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.0205</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.6256</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.2769</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.5874999999999999</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>entropy appliance-vec</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>{"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Example-Guided_LLM_Scoring</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>0.2957</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.5026</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.7641</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.2769</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.5874999999999999</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>entropy appliance-vec</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>{"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>0.8832</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.8995</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.9072</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.9794</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.2769</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.5874999999999999</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>entropy shower-vec</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>{"energy_cost": 0.333611, "environmental": 0.313969, "comfort": 0.126582, "practicality": 0.225838}</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Direct_LLM_Scoring</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>0.0769</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.0872</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.2564</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.5533000000000001</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>entropy shower-vec</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>{"energy_cost": 0.333611, "environmental": 0.313969, "comfort": 0.126582, "practicality": 0.225838}</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Example-Guided_LLM_Scoring</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.5179</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.7846</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.2564</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.5533000000000001</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>entropy shower-vec</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>{"energy_cost": 0.333611, "environmental": 0.313969, "comfort": 0.126582, "practicality": 0.225838}</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>0.8866000000000001</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.9072</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.9072</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.9845</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.2564</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.5533000000000001</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>entropy per-type</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.333611, "environmental": 0.313969, "comfort": 0.126582, "practicality": 0.225838}}</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Direct_LLM_Scoring</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>0.0496</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.0564</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.6615</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.2872</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.5635</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>entropy per-type</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.333611, "environmental": 0.313969, "comfort": 0.126582, "practicality": 0.225838}}</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Example-Guided_LLM_Scoring</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.5538</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.7897</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.2872</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.5635</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>entropy per-type</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.333611, "environmental": 0.313969, "comfort": 0.126582, "practicality": 0.225838}}</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>0.9003</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.9227</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.9485</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.9948</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.2872</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.5635</v>
       </c>
     </row>
   </sheetData>

--- a/Output Files GPT-OSS 20B/sensitivity_analysis_gptoss.xlsx
+++ b/Output Files GPT-OSS 20B/sensitivity_analysis_gptoss.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J61"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,22 +490,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.053</v>
+        <v>0.04068000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>0.059</v>
+        <v>0.03845999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3385</v>
+        <v>0.33334</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6513</v>
+        <v>0.66462</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3214</v>
+        <v>0.22974</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5327999999999999</v>
+        <v>0.62624</v>
       </c>
     </row>
     <row r="3">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.3744</v>
+        <v>0.27042</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3821</v>
+        <v>0.28974</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5641</v>
+        <v>0.48</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7795</v>
+        <v>0.76922</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3214</v>
+        <v>0.22974</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5327999999999999</v>
+        <v>0.62624</v>
       </c>
     </row>
     <row r="4">
@@ -570,22 +570,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9072</v>
+        <v>0.89666</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9201</v>
+        <v>0.9107799999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9227</v>
+        <v>0.91616</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9897</v>
+        <v>0.9812799999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3214</v>
+        <v>0.22974</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5327999999999999</v>
+        <v>0.62624</v>
       </c>
     </row>
     <row r="5">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.0803</v>
+        <v>0.08033999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1</v>
+        <v>0.08874</v>
       </c>
       <c r="G5" t="n">
-        <v>0.359</v>
+        <v>0.3672</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6872</v>
+        <v>0.70564</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3146</v>
+        <v>0.227</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5089000000000001</v>
+        <v>0.5823</v>
       </c>
     </row>
     <row r="6">
@@ -650,22 +650,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.3949</v>
+        <v>0.3073399999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4077</v>
+        <v>0.33024</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5846</v>
+        <v>0.50668</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8</v>
+        <v>0.7918000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3146</v>
+        <v>0.227</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5089000000000001</v>
+        <v>0.5823</v>
       </c>
     </row>
     <row r="7">
@@ -690,22 +690,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9038</v>
+        <v>0.88964</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9175</v>
+        <v>0.9061</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9175</v>
+        <v>0.9020999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9845</v>
+        <v>0.98712</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3146</v>
+        <v>0.227</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5089000000000001</v>
+        <v>0.5823</v>
       </c>
     </row>
     <row r="8">
@@ -730,22 +730,22 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.0803</v>
+        <v>0.05026000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0897</v>
+        <v>0.04973999999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3641</v>
+        <v>0.34052</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6667</v>
+        <v>0.68102</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2394</v>
+        <v>0.20242</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5978</v>
+        <v>0.63628</v>
       </c>
     </row>
     <row r="9">
@@ -770,22 +770,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.3197</v>
+        <v>0.25268</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3359</v>
+        <v>0.26924</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5385</v>
+        <v>0.47078</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7744</v>
+        <v>0.77128</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2394</v>
+        <v>0.20242</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5978</v>
+        <v>0.63628</v>
       </c>
     </row>
     <row r="10">
@@ -810,22 +810,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9175</v>
+        <v>0.88896</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9356</v>
+        <v>0.9050800000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.91964</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0.9941600000000002</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2394</v>
+        <v>0.20242</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5978</v>
+        <v>0.63628</v>
       </c>
     </row>
     <row r="11">
@@ -850,22 +850,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.0496</v>
+        <v>0.05366</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0615</v>
+        <v>0.0554</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3333</v>
+        <v>0.34768</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6564</v>
+        <v>0.6799999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3419</v>
+        <v>0.24686</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5226</v>
+        <v>0.5992</v>
       </c>
     </row>
     <row r="12">
@@ -890,22 +890,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.3915</v>
+        <v>0.30052</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4051</v>
+        <v>0.32</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5744</v>
+        <v>0.50154</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7846</v>
+        <v>0.7784799999999998</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3419</v>
+        <v>0.24686</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5226</v>
+        <v>0.5992</v>
       </c>
     </row>
     <row r="13">
@@ -930,22 +930,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9141</v>
+        <v>0.89972</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9278</v>
+        <v>0.91838</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9278</v>
+        <v>0.90798</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9845</v>
+        <v>0.98712</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3419</v>
+        <v>0.24686</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5226</v>
+        <v>0.5992</v>
       </c>
     </row>
     <row r="14">
@@ -970,22 +970,22 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.0906</v>
+        <v>0.05708000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0949</v>
+        <v>0.05644</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3641</v>
+        <v>0.33948</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6768999999999999</v>
+        <v>0.6881999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2462</v>
+        <v>0.1975999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>0.591</v>
+        <v>0.64516</v>
       </c>
     </row>
     <row r="15">
@@ -1010,22 +1010,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.3368</v>
+        <v>0.25468</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3487</v>
+        <v>0.27076</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5385</v>
+        <v>0.4656399999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7795</v>
+        <v>0.7702800000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2462</v>
+        <v>0.1975999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>0.591</v>
+        <v>0.64516</v>
       </c>
     </row>
     <row r="16">
@@ -1050,22 +1050,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9278</v>
+        <v>0.89984</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9459</v>
+        <v>0.9156000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9433</v>
+        <v>0.9243399999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0.9941600000000002</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2462</v>
+        <v>0.1975999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>0.591</v>
+        <v>0.64516</v>
       </c>
     </row>
     <row r="17">
@@ -1090,22 +1090,22 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.0803</v>
+        <v>0.04820000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0872</v>
+        <v>0.04564</v>
       </c>
       <c r="G17" t="n">
-        <v>0.359</v>
+        <v>0.3333199999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6768999999999999</v>
+        <v>0.68102</v>
       </c>
       <c r="I17" t="n">
-        <v>0.277</v>
+        <v>0.22428</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5568</v>
+        <v>0.6266</v>
       </c>
     </row>
     <row r="18">
@@ -1130,22 +1130,22 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.3573</v>
+        <v>0.27248</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3744</v>
+        <v>0.2892400000000001</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5538</v>
+        <v>0.4759</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7949000000000001</v>
+        <v>0.7764</v>
       </c>
       <c r="I18" t="n">
-        <v>0.277</v>
+        <v>0.22428</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5568</v>
+        <v>0.6266</v>
       </c>
     </row>
     <row r="19">
@@ -1170,22 +1170,22 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9141</v>
+        <v>0.89908</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9304</v>
+        <v>0.91088</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9433</v>
+        <v>0.92778</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9948</v>
+        <v>0.9907</v>
       </c>
       <c r="I19" t="n">
-        <v>0.277</v>
+        <v>0.22428</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5568</v>
+        <v>0.6266</v>
       </c>
     </row>
     <row r="20">
@@ -1210,22 +1210,22 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.0974</v>
+        <v>0.06804</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1128</v>
+        <v>0.07382</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3795</v>
+        <v>0.36</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6923</v>
+        <v>0.69336</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2838</v>
+        <v>0.23726</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4951</v>
+        <v>0.58042</v>
       </c>
     </row>
     <row r="21">
@@ -1250,22 +1250,22 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.3812</v>
+        <v>0.3053</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3846</v>
+        <v>0.32052</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.50258</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7795</v>
+        <v>0.77742</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2838</v>
+        <v>0.23726</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4951</v>
+        <v>0.58042</v>
       </c>
     </row>
     <row r="22">
@@ -1290,22 +1290,22 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.8763</v>
+        <v>0.8857200000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8918</v>
+        <v>0.90084</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9021</v>
+        <v>0.90784</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9794</v>
+        <v>0.98248</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2838</v>
+        <v>0.23726</v>
       </c>
       <c r="J22" t="n">
-        <v>0.4951</v>
+        <v>0.58042</v>
       </c>
     </row>
     <row r="23">
@@ -1330,22 +1330,22 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.0769</v>
+        <v>0.04754</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0795</v>
+        <v>0.04974</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3641</v>
+        <v>0.34358</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6667</v>
+        <v>0.6851199999999998</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2496</v>
+        <v>0.20444</v>
       </c>
       <c r="J23" t="n">
-        <v>0.5979</v>
+        <v>0.6471399999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1370,22 +1370,22 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.3265</v>
+        <v>0.25198</v>
       </c>
       <c r="F24" t="n">
-        <v>0.3385</v>
+        <v>0.26614</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5282</v>
+        <v>0.46256</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7744</v>
+        <v>0.76306</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2496</v>
+        <v>0.20444</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5979</v>
+        <v>0.6471399999999999</v>
       </c>
     </row>
     <row r="25">
@@ -1410,22 +1410,22 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9244</v>
+        <v>0.8991199999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9407</v>
+        <v>0.91792</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9485</v>
+        <v>0.92322</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0.9941600000000002</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2496</v>
+        <v>0.20444</v>
       </c>
       <c r="J25" t="n">
-        <v>0.5979</v>
+        <v>0.6471399999999999</v>
       </c>
     </row>
     <row r="26">
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.0564</v>
+        <v>0.05574000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0692</v>
+        <v>0.05848</v>
       </c>
       <c r="G26" t="n">
-        <v>0.3436</v>
+        <v>0.34666</v>
       </c>
       <c r="H26" t="n">
-        <v>0.6667</v>
+        <v>0.68308</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3351</v>
+        <v>0.25776</v>
       </c>
       <c r="J26" t="n">
-        <v>0.5398000000000001</v>
+        <v>0.5970399999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1490,22 +1490,22 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.3915</v>
+        <v>0.3135</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4051</v>
+        <v>0.33334</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5846</v>
+        <v>0.5158800000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7846</v>
+        <v>0.7795</v>
       </c>
       <c r="I27" t="n">
-        <v>0.3351</v>
+        <v>0.25776</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5398000000000001</v>
+        <v>0.5970399999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1530,22 +1530,22 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.9313</v>
+        <v>0.9105399999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9433</v>
+        <v>0.92644</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9381</v>
+        <v>0.9206999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9897</v>
+        <v>0.98712</v>
       </c>
       <c r="I28" t="n">
-        <v>0.3351</v>
+        <v>0.25776</v>
       </c>
       <c r="J28" t="n">
-        <v>0.5398000000000001</v>
+        <v>0.5970399999999999</v>
       </c>
     </row>
     <row r="29">
@@ -1570,22 +1570,22 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.1419</v>
+        <v>0.07896</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1538</v>
+        <v>0.08819999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>0.441</v>
+        <v>0.37744</v>
       </c>
       <c r="H29" t="n">
-        <v>0.7128</v>
+        <v>0.7066800000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1949</v>
+        <v>0.20174</v>
       </c>
       <c r="J29" t="n">
-        <v>0.5670000000000001</v>
+        <v>0.6105400000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1610,22 +1610,22 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.3368</v>
+        <v>0.2807</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3615</v>
+        <v>0.29436</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5538</v>
+        <v>0.49436</v>
       </c>
       <c r="H30" t="n">
-        <v>0.7795</v>
+        <v>0.77642</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1949</v>
+        <v>0.20174</v>
       </c>
       <c r="J30" t="n">
-        <v>0.5670000000000001</v>
+        <v>0.6105400000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1650,22 +1650,22 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9038</v>
+        <v>0.89124</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9227</v>
+        <v>0.91028</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9485</v>
+        <v>0.9348000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9897</v>
+        <v>0.9836599999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1949</v>
+        <v>0.20174</v>
       </c>
       <c r="J31" t="n">
-        <v>0.5670000000000001</v>
+        <v>0.6105400000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.19356, "environmental": 0.131075, "comfort": 0.40357, "practicality": 0.271796}</t>
+          <t>{"energy_cost": 0.194172, "environmental": 0.131673, "comfort": 0.401912, "practicality": 0.272243}</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1690,22 +1690,22 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.3436</v>
+        <v>0.2335</v>
       </c>
       <c r="F32" t="n">
-        <v>0.359</v>
+        <v>0.25384</v>
       </c>
       <c r="G32" t="n">
-        <v>0.5231</v>
+        <v>0.46872</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8154</v>
+        <v>0.77434</v>
       </c>
       <c r="I32" t="n">
-        <v>0.04099999999999998</v>
+        <v>0.09777999999999998</v>
       </c>
       <c r="J32" t="n">
-        <v>0.5535000000000001</v>
+        <v>0.59806</v>
       </c>
     </row>
     <row r="33">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.19356, "environmental": 0.131075, "comfort": 0.40357, "practicality": 0.271796}</t>
+          <t>{"energy_cost": 0.194172, "environmental": 0.131673, "comfort": 0.401912, "practicality": 0.272243}</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1730,22 +1730,22 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.3846</v>
+        <v>0.33128</v>
       </c>
       <c r="F33" t="n">
-        <v>0.4128</v>
+        <v>0.3527999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>0.5949</v>
+        <v>0.53538</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8051</v>
+        <v>0.8</v>
       </c>
       <c r="I33" t="n">
-        <v>0.04099999999999998</v>
+        <v>0.09777999999999998</v>
       </c>
       <c r="J33" t="n">
-        <v>0.5535000000000001</v>
+        <v>0.59806</v>
       </c>
     </row>
     <row r="34">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.19356, "environmental": 0.131075, "comfort": 0.40357, "practicality": 0.271796}</t>
+          <t>{"energy_cost": 0.194172, "environmental": 0.131673, "comfort": 0.401912, "practicality": 0.272243}</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1770,22 +1770,22 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9381</v>
+        <v>0.9293400000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9536</v>
+        <v>0.94702</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9227</v>
+        <v>0.9091800000000001</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>0.04099999999999998</v>
+        <v>0.09777999999999998</v>
       </c>
       <c r="J34" t="n">
-        <v>0.5535000000000001</v>
+        <v>0.59806</v>
       </c>
     </row>
     <row r="35">
@@ -1810,22 +1810,22 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.3436</v>
+        <v>0.27452</v>
       </c>
       <c r="F35" t="n">
-        <v>0.3615</v>
+        <v>0.3005</v>
       </c>
       <c r="G35" t="n">
-        <v>0.5333</v>
+        <v>0.49128</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8</v>
+        <v>0.79078</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2085</v>
+        <v>0.1661799999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>0.4101</v>
+        <v>0.5196999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -1850,22 +1850,22 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.5521</v>
+        <v>0.4407</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5769</v>
+        <v>0.4646199999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>0.6667</v>
+        <v>0.61026</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8821</v>
+        <v>0.8359</v>
       </c>
       <c r="I36" t="n">
-        <v>0.2085</v>
+        <v>0.1661799999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>0.4101</v>
+        <v>0.5196999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -1890,22 +1890,22 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.9622000000000001</v>
+        <v>0.9603999999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9716</v>
+        <v>0.97028</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9485</v>
+        <v>0.9464399999999999</v>
       </c>
       <c r="H37" t="n">
         <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2085</v>
+        <v>0.1661799999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>0.4101</v>
+        <v>0.5196999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1930,22 +1930,22 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.306</v>
+        <v>0.1911</v>
       </c>
       <c r="F38" t="n">
-        <v>0.3333</v>
+        <v>0.21334</v>
       </c>
       <c r="G38" t="n">
-        <v>0.4821</v>
+        <v>0.42666</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8256</v>
+        <v>0.7640999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>0.01019999999999999</v>
+        <v>0.07999999999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>0.6219000000000001</v>
+        <v>0.6575</v>
       </c>
     </row>
     <row r="39">
@@ -1970,22 +1970,22 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.3162</v>
+        <v>0.2711</v>
       </c>
       <c r="F39" t="n">
-        <v>0.3436</v>
+        <v>0.28566</v>
       </c>
       <c r="G39" t="n">
-        <v>0.5231</v>
+        <v>0.48206</v>
       </c>
       <c r="H39" t="n">
-        <v>0.7846</v>
+        <v>0.7835799999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>0.01019999999999999</v>
+        <v>0.07999999999999999</v>
       </c>
       <c r="J39" t="n">
-        <v>0.6219000000000001</v>
+        <v>0.6575</v>
       </c>
     </row>
     <row r="40">
@@ -2010,22 +2010,22 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.9381</v>
+        <v>0.9286</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9536</v>
+        <v>0.9458800000000001</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9278</v>
+        <v>0.92552</v>
       </c>
       <c r="H40" t="n">
-        <v>1</v>
+        <v>0.99886</v>
       </c>
       <c r="I40" t="n">
-        <v>0.01019999999999999</v>
+        <v>0.07999999999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>0.6219000000000001</v>
+        <v>0.6575</v>
       </c>
     </row>
     <row r="41">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.248147, "environmental": 0.24439, "comfort": 0.202824, "practicality": 0.304639}</t>
+          <t>{"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2050,22 +2050,22 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.1521</v>
+        <v>0.07146</v>
       </c>
       <c r="F41" t="n">
-        <v>0.1641</v>
+        <v>0.08</v>
       </c>
       <c r="G41" t="n">
-        <v>0.4462</v>
+        <v>0.37436</v>
       </c>
       <c r="H41" t="n">
-        <v>0.7128</v>
+        <v>0.69948</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1744</v>
+        <v>0.1935</v>
       </c>
       <c r="J41" t="n">
-        <v>0.5704</v>
+        <v>0.6169600000000001</v>
       </c>
     </row>
     <row r="42">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.248147, "environmental": 0.24439, "comfort": 0.202824, "practicality": 0.304639}</t>
+          <t>{"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2090,22 +2090,22 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.3265</v>
+        <v>0.26496</v>
       </c>
       <c r="F42" t="n">
-        <v>0.3487</v>
+        <v>0.2795</v>
       </c>
       <c r="G42" t="n">
-        <v>0.5385</v>
+        <v>0.48102</v>
       </c>
       <c r="H42" t="n">
-        <v>0.7846</v>
+        <v>0.76922</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1744</v>
+        <v>0.1935</v>
       </c>
       <c r="J42" t="n">
-        <v>0.5704</v>
+        <v>0.6169600000000001</v>
       </c>
     </row>
     <row r="43">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.248147, "environmental": 0.24439, "comfort": 0.202824, "practicality": 0.304639}</t>
+          <t>{"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2130,22 +2130,22 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.8969</v>
+        <v>0.88192</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9175</v>
+        <v>0.9026799999999999</v>
       </c>
       <c r="G43" t="n">
-        <v>0.9330000000000001</v>
+        <v>0.9196</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9897</v>
+        <v>0.9836599999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1744</v>
+        <v>0.1935</v>
       </c>
       <c r="J43" t="n">
-        <v>0.5704</v>
+        <v>0.6169600000000001</v>
       </c>
     </row>
     <row r="44">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.248147, "environmental": 0.24439, "comfort": 0.202824, "practicality": 0.304639}}</t>
+          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}}</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2170,22 +2170,22 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.2581</v>
+        <v>0.16168</v>
       </c>
       <c r="F44" t="n">
-        <v>0.2744</v>
+        <v>0.18358</v>
       </c>
       <c r="G44" t="n">
-        <v>0.4615</v>
+        <v>0.41434</v>
       </c>
       <c r="H44" t="n">
-        <v>0.7641</v>
+        <v>0.74154</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2017</v>
+        <v>0.2249800000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>0.468</v>
+        <v>0.5208999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.248147, "environmental": 0.24439, "comfort": 0.202824, "practicality": 0.304639}}</t>
+          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}}</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2210,22 +2210,22 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.4598</v>
+        <v>0.3866600000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4821</v>
+        <v>0.4097399999999999</v>
       </c>
       <c r="G45" t="n">
-        <v>0.6359</v>
+        <v>0.57128</v>
       </c>
       <c r="H45" t="n">
-        <v>0.841</v>
+        <v>0.8348799999999998</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2017</v>
+        <v>0.2249800000000001</v>
       </c>
       <c r="J45" t="n">
-        <v>0.468</v>
+        <v>0.5208999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.248147, "environmental": 0.24439, "comfort": 0.202824, "practicality": 0.304639}}</t>
+          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}}</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2250,22 +2250,22 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.9278</v>
+        <v>0.9075599999999999</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9407</v>
+        <v>0.9219200000000001</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9433</v>
+        <v>0.9277599999999999</v>
       </c>
       <c r="H46" t="n">
-        <v>0.9897</v>
+        <v>0.9836599999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2017</v>
+        <v>0.2249800000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>0.468</v>
+        <v>0.5208999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.268298, "environmental": 0.370515, "comfort": 0.162689, "practicality": 0.198498}</t>
+          <t>{"energy_cost": 0.268909, "environmental": 0.371359, "comfort": 0.160782, "practicality": 0.19895}</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2290,22 +2290,22 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.0803</v>
+        <v>0.0393</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0897</v>
+        <v>0.04102</v>
       </c>
       <c r="G47" t="n">
-        <v>0.3487</v>
+        <v>0.33846</v>
       </c>
       <c r="H47" t="n">
-        <v>0.6768999999999999</v>
+        <v>0.6707799999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2701</v>
+        <v>0.22908</v>
       </c>
       <c r="J47" t="n">
-        <v>0.5362</v>
+        <v>0.6012000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.268298, "environmental": 0.370515, "comfort": 0.162689, "practicality": 0.198498}</t>
+          <t>{"energy_cost": 0.268909, "environmental": 0.371359, "comfort": 0.160782, "practicality": 0.19895}</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2330,22 +2330,22 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.3504</v>
+        <v>0.26838</v>
       </c>
       <c r="F48" t="n">
-        <v>0.3538</v>
+        <v>0.27948</v>
       </c>
       <c r="G48" t="n">
-        <v>0.5385</v>
+        <v>0.48</v>
       </c>
       <c r="H48" t="n">
-        <v>0.7846</v>
+        <v>0.7702600000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2701</v>
+        <v>0.22908</v>
       </c>
       <c r="J48" t="n">
-        <v>0.5362</v>
+        <v>0.6012000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.268298, "environmental": 0.370515, "comfort": 0.162689, "practicality": 0.198498}</t>
+          <t>{"energy_cost": 0.268909, "environmental": 0.371359, "comfort": 0.160782, "practicality": 0.19895}</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2370,22 +2370,22 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.8866000000000001</v>
+        <v>0.86958</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9046</v>
+        <v>0.8876200000000001</v>
       </c>
       <c r="G49" t="n">
-        <v>0.9278</v>
+        <v>0.90572</v>
       </c>
       <c r="H49" t="n">
-        <v>0.9794</v>
+        <v>0.9812999999999998</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2701</v>
+        <v>0.22908</v>
       </c>
       <c r="J49" t="n">
-        <v>0.5362</v>
+        <v>0.6012000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2410,22 +2410,22 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.0701</v>
+        <v>0.05572000000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.05692000000000001</v>
       </c>
       <c r="G50" t="n">
-        <v>0.3436</v>
+        <v>0.34256</v>
       </c>
       <c r="H50" t="n">
-        <v>0.6821</v>
+        <v>0.68206</v>
       </c>
       <c r="I50" t="n">
-        <v>0.3248</v>
+        <v>0.25642</v>
       </c>
       <c r="J50" t="n">
-        <v>0.5054000000000001</v>
+        <v>0.5672999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -2450,22 +2450,22 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.3949</v>
+        <v>0.31214</v>
       </c>
       <c r="F51" t="n">
-        <v>0.4154</v>
+        <v>0.3318</v>
       </c>
       <c r="G51" t="n">
-        <v>0.5846</v>
+        <v>0.5117800000000001</v>
       </c>
       <c r="H51" t="n">
-        <v>0.8</v>
+        <v>0.78768</v>
       </c>
       <c r="I51" t="n">
-        <v>0.3248</v>
+        <v>0.25642</v>
       </c>
       <c r="J51" t="n">
-        <v>0.5054000000000001</v>
+        <v>0.5672999999999999</v>
       </c>
     </row>
     <row r="52">
@@ -2490,22 +2490,22 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.9003</v>
+        <v>0.87944</v>
       </c>
       <c r="F52" t="n">
-        <v>0.9175</v>
+        <v>0.8985199999999999</v>
       </c>
       <c r="G52" t="n">
-        <v>0.9227</v>
+        <v>0.89394</v>
       </c>
       <c r="H52" t="n">
-        <v>0.9897</v>
+        <v>0.98942</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3248</v>
+        <v>0.25642</v>
       </c>
       <c r="J52" t="n">
-        <v>0.5054000000000001</v>
+        <v>0.5672999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -2530,22 +2530,22 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.0188</v>
+        <v>0.004459999999999999</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0205</v>
+        <v>0.004119999999999999</v>
       </c>
       <c r="G53" t="n">
-        <v>0.3333</v>
+        <v>0.33024</v>
       </c>
       <c r="H53" t="n">
-        <v>0.6256</v>
+        <v>0.63486</v>
       </c>
       <c r="I53" t="n">
-        <v>0.2769</v>
+        <v>0.23658</v>
       </c>
       <c r="J53" t="n">
-        <v>0.5874999999999999</v>
+        <v>0.62146</v>
       </c>
     </row>
     <row r="54">
@@ -2570,22 +2570,22 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.2957</v>
+        <v>0.24104</v>
       </c>
       <c r="F54" t="n">
-        <v>0.3</v>
+        <v>0.24974</v>
       </c>
       <c r="G54" t="n">
-        <v>0.5026</v>
+        <v>0.47074</v>
       </c>
       <c r="H54" t="n">
-        <v>0.7641</v>
+        <v>0.75588</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2769</v>
+        <v>0.23658</v>
       </c>
       <c r="J54" t="n">
-        <v>0.5874999999999999</v>
+        <v>0.62146</v>
       </c>
     </row>
     <row r="55">
@@ -2610,22 +2610,22 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.8832</v>
+        <v>0.8625</v>
       </c>
       <c r="F55" t="n">
-        <v>0.8995</v>
+        <v>0.8793799999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>0.9072</v>
+        <v>0.89276</v>
       </c>
       <c r="H55" t="n">
-        <v>0.9794</v>
+        <v>0.97898</v>
       </c>
       <c r="I55" t="n">
-        <v>0.2769</v>
+        <v>0.23658</v>
       </c>
       <c r="J55" t="n">
-        <v>0.5874999999999999</v>
+        <v>0.62146</v>
       </c>
     </row>
     <row r="56">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.333611, "environmental": 0.313969, "comfort": 0.126582, "practicality": 0.225838}</t>
+          <t>{"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2650,22 +2650,22 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.0769</v>
+        <v>0.05028000000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>0.0872</v>
+        <v>0.05744</v>
       </c>
       <c r="G56" t="n">
-        <v>0.3436</v>
+        <v>0.34154</v>
       </c>
       <c r="H56" t="n">
-        <v>0.6667</v>
+        <v>0.6677</v>
       </c>
       <c r="I56" t="n">
-        <v>0.2564</v>
+        <v>0.2304</v>
       </c>
       <c r="J56" t="n">
-        <v>0.5533000000000001</v>
+        <v>0.5647</v>
       </c>
     </row>
     <row r="57">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.333611, "environmental": 0.313969, "comfort": 0.126582, "practicality": 0.225838}</t>
+          <t>{"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2690,22 +2690,22 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.3333</v>
+        <v>0.28068</v>
       </c>
       <c r="F57" t="n">
-        <v>0.3436</v>
+        <v>0.29744</v>
       </c>
       <c r="G57" t="n">
-        <v>0.5179</v>
+        <v>0.4851200000000001</v>
       </c>
       <c r="H57" t="n">
-        <v>0.7846</v>
+        <v>0.7712600000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2564</v>
+        <v>0.2304</v>
       </c>
       <c r="J57" t="n">
-        <v>0.5533000000000001</v>
+        <v>0.5647</v>
       </c>
     </row>
     <row r="58">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.333611, "environmental": 0.313969, "comfort": 0.126582, "practicality": 0.225838}</t>
+          <t>{"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2730,22 +2730,22 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.8866000000000001</v>
+        <v>0.8453799999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>0.9072</v>
+        <v>0.8689</v>
       </c>
       <c r="G58" t="n">
-        <v>0.9072</v>
+        <v>0.8648199999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>0.9845</v>
+        <v>0.98016</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2564</v>
+        <v>0.2304</v>
       </c>
       <c r="J58" t="n">
-        <v>0.5533000000000001</v>
+        <v>0.5647</v>
       </c>
     </row>
     <row r="59">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.333611, "environmental": 0.313969, "comfort": 0.126582, "practicality": 0.225838}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}}</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2770,22 +2770,22 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.0496</v>
+        <v>0.03932</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0564</v>
+        <v>0.0364</v>
       </c>
       <c r="G59" t="n">
-        <v>0.3487</v>
+        <v>0.34562</v>
       </c>
       <c r="H59" t="n">
-        <v>0.6615</v>
+        <v>0.67284</v>
       </c>
       <c r="I59" t="n">
-        <v>0.2872</v>
+        <v>0.23452</v>
       </c>
       <c r="J59" t="n">
-        <v>0.5635</v>
+        <v>0.6103799999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.333611, "environmental": 0.313969, "comfort": 0.126582, "practicality": 0.225838}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}}</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2810,22 +2810,22 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.3368</v>
+        <v>0.27384</v>
       </c>
       <c r="F60" t="n">
-        <v>0.3513</v>
+        <v>0.28566</v>
       </c>
       <c r="G60" t="n">
-        <v>0.5538</v>
+        <v>0.49024</v>
       </c>
       <c r="H60" t="n">
-        <v>0.7897</v>
+        <v>0.77846</v>
       </c>
       <c r="I60" t="n">
-        <v>0.2872</v>
+        <v>0.23452</v>
       </c>
       <c r="J60" t="n">
-        <v>0.5635</v>
+        <v>0.6103799999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.333611, "environmental": 0.313969, "comfort": 0.126582, "practicality": 0.225838}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}}</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2850,22 +2850,502 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.9003</v>
+        <v>0.88422</v>
       </c>
       <c r="F61" t="n">
-        <v>0.9227</v>
+        <v>0.9009</v>
       </c>
       <c r="G61" t="n">
-        <v>0.9485</v>
+        <v>0.93008</v>
       </c>
       <c r="H61" t="n">
-        <v>0.9948</v>
+        <v>0.9859599999999998</v>
       </c>
       <c r="I61" t="n">
-        <v>0.2872</v>
+        <v>0.23452</v>
       </c>
       <c r="J61" t="n">
-        <v>0.5635</v>
+        <v>0.6103799999999999</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>merec hvac-type only</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>{"HVAC": {"energy_cost": 0.138, "environmental": 0.128, "comfort": 0.663, "practicality": 0.071}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}}</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Direct_LLM_Scoring</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0.07211999999999999</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.07692</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.67798</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.29336</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.5467200000000001</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>merec hvac-type only</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>{"HVAC": {"energy_cost": 0.138, "environmental": 0.128, "comfort": 0.663, "practicality": 0.071}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}}</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Example-Guided_LLM_Scoring</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0.36548</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.3845999999999999</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.5518000000000001</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.8194799999999999</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.29336</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.5467200000000001</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>merec hvac-type only</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>{"HVAC": {"energy_cost": 0.138, "environmental": 0.128, "comfort": 0.663, "practicality": 0.071}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}}</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0.9122</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.9224399999999999</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.93244</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.9812799999999999</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.29336</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.5467200000000001</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>merec appliance-type only</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.208, "environmental": 0.044, "comfort": 0.292, "practicality": 0.456}, "Shower": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}}</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Direct_LLM_Scoring</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>0.06598</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.07126</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.6882200000000001</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.25368</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.5893999999999999</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>merec appliance-type only</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.208, "environmental": 0.044, "comfort": 0.292, "practicality": 0.456}, "Shower": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}}</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Example-Guided_LLM_Scoring</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.34616</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.51384</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.25368</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.5893999999999999</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>merec appliance-type only</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.208, "environmental": 0.044, "comfort": 0.292, "practicality": 0.456}, "Shower": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}}</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>0.90906</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.92012</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.92078</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.9812799999999999</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.25368</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.5893999999999999</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>merec shower-type only</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.248, "environmental": 0.244, "comfort": 0.203, "practicality": 0.305}}</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Direct_LLM_Scoring</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>0.11316</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.11998</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.39076</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.70974</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.13058</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.6389999999999998</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>merec shower-type only</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.248, "environmental": 0.244, "comfort": 0.203, "practicality": 0.305}}</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Example-Guided_LLM_Scoring</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>0.24374</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.26052</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.46872</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.7558999999999999</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.13058</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.6389999999999998</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>merec shower-type only</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.248, "environmental": 0.244, "comfort": 0.203, "practicality": 0.305}}</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>0.8827399999999999</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.9026999999999999</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.91264</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.9836599999999999</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.13058</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.6389999999999998</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>entropy per-type (tab)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.333666, "environmental": 0.313686, "comfort": 0.126873, "practicality": 0.225774}}</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Direct_LLM_Scoring</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>0.04072</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.03793999999999999</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.6748800000000001</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.23176</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.6125</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>entropy per-type (tab)</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.333666, "environmental": 0.313686, "comfort": 0.126873, "practicality": 0.225774}}</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Example-Guided_LLM_Scoring</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>0.27248</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.28462</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.4892</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.77846</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.23176</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.6125</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>entropy per-type (tab)</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.333666, "environmental": 0.313686, "comfort": 0.126873, "practicality": 0.225774}}</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LLM-Parameterized_Reference_Scoring</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>0.88498</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.90266</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.9289400000000001</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.9882799999999999</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.23176</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.6125</v>
       </c>
     </row>
   </sheetData>

--- a/Output Files GPT-OSS 20B/sensitivity_analysis_gptoss.xlsx
+++ b/Output Files GPT-OSS 20B/sensitivity_analysis_gptoss.xlsx
@@ -502,10 +502,10 @@
         <v>0.66462</v>
       </c>
       <c r="I2" t="n">
-        <v>0.22974</v>
+        <v>0.2318</v>
       </c>
       <c r="J2" t="n">
-        <v>0.62624</v>
+        <v>0.6249600000000002</v>
       </c>
     </row>
     <row r="3">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.27042</v>
+        <v>0.2724799999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.28974</v>
+        <v>0.29076</v>
       </c>
       <c r="G3" t="n">
-        <v>0.48</v>
+        <v>0.47386</v>
       </c>
       <c r="H3" t="n">
-        <v>0.76922</v>
+        <v>0.7651199999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.22974</v>
+        <v>0.2318</v>
       </c>
       <c r="J3" t="n">
-        <v>0.62624</v>
+        <v>0.6249600000000002</v>
       </c>
     </row>
     <row r="4">
@@ -570,22 +570,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.89666</v>
+        <v>0.8974400000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9107799999999999</v>
+        <v>0.9113599999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>0.91616</v>
+        <v>0.9173</v>
       </c>
       <c r="H4" t="n">
         <v>0.9812799999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.22974</v>
+        <v>0.2318</v>
       </c>
       <c r="J4" t="n">
-        <v>0.62624</v>
+        <v>0.6249600000000002</v>
       </c>
     </row>
     <row r="5">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.08033999999999999</v>
+        <v>0.08102000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>0.08874</v>
+        <v>0.08972000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3672</v>
+        <v>0.36924</v>
       </c>
       <c r="H5" t="n">
-        <v>0.70564</v>
+        <v>0.7056600000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>0.227</v>
+        <v>0.22704</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5823</v>
+        <v>0.5847</v>
       </c>
     </row>
     <row r="6">
@@ -650,22 +650,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.3073399999999999</v>
+        <v>0.30806</v>
       </c>
       <c r="F6" t="n">
-        <v>0.33024</v>
+        <v>0.32668</v>
       </c>
       <c r="G6" t="n">
-        <v>0.50668</v>
+        <v>0.5005000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7918000000000001</v>
+        <v>0.7866799999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.227</v>
+        <v>0.22704</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5823</v>
+        <v>0.5847</v>
       </c>
     </row>
     <row r="7">
@@ -690,22 +690,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.88964</v>
+        <v>0.89276</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9061</v>
+        <v>0.90848</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9020999999999999</v>
+        <v>0.90564</v>
       </c>
       <c r="H7" t="n">
         <v>0.98712</v>
       </c>
       <c r="I7" t="n">
-        <v>0.227</v>
+        <v>0.22704</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5823</v>
+        <v>0.5847</v>
       </c>
     </row>
     <row r="8">
@@ -730,10 +730,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.05026000000000001</v>
+        <v>0.0523</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04973999999999999</v>
+        <v>0.0518</v>
       </c>
       <c r="G8" t="n">
         <v>0.34052</v>
@@ -742,10 +742,10 @@
         <v>0.68102</v>
       </c>
       <c r="I8" t="n">
-        <v>0.20242</v>
+        <v>0.22084</v>
       </c>
       <c r="J8" t="n">
-        <v>0.63628</v>
+        <v>0.61894</v>
       </c>
     </row>
     <row r="9">
@@ -770,22 +770,22 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.25268</v>
+        <v>0.27314</v>
       </c>
       <c r="F9" t="n">
-        <v>0.26924</v>
+        <v>0.2882000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>0.47078</v>
+        <v>0.48206</v>
       </c>
       <c r="H9" t="n">
         <v>0.77128</v>
       </c>
       <c r="I9" t="n">
-        <v>0.20242</v>
+        <v>0.22084</v>
       </c>
       <c r="J9" t="n">
-        <v>0.63628</v>
+        <v>0.61894</v>
       </c>
     </row>
     <row r="10">
@@ -810,22 +810,22 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.88896</v>
+        <v>0.89208</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9050800000000001</v>
+        <v>0.9068400000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>0.91964</v>
+        <v>0.92548</v>
       </c>
       <c r="H10" t="n">
         <v>0.9941600000000002</v>
       </c>
       <c r="I10" t="n">
-        <v>0.20242</v>
+        <v>0.22084</v>
       </c>
       <c r="J10" t="n">
-        <v>0.63628</v>
+        <v>0.61894</v>
       </c>
     </row>
     <row r="11">
@@ -850,22 +850,22 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.05366</v>
+        <v>0.05776</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0554</v>
+        <v>0.06052</v>
       </c>
       <c r="G11" t="n">
-        <v>0.34768</v>
+        <v>0.3497400000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6799999999999999</v>
+        <v>0.6800200000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>0.24686</v>
+        <v>0.23796</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5992</v>
+        <v>0.6024799999999999</v>
       </c>
     </row>
     <row r="12">
@@ -890,22 +890,22 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.30052</v>
+        <v>0.29572</v>
       </c>
       <c r="F12" t="n">
-        <v>0.32</v>
+        <v>0.31282</v>
       </c>
       <c r="G12" t="n">
-        <v>0.50154</v>
+        <v>0.49128</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7784799999999998</v>
+        <v>0.7733399999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.24686</v>
+        <v>0.23796</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5992</v>
+        <v>0.6024799999999999</v>
       </c>
     </row>
     <row r="13">
@@ -930,22 +930,22 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.89972</v>
+        <v>0.8981999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>0.91838</v>
+        <v>0.9149200000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>0.90798</v>
+        <v>0.91152</v>
       </c>
       <c r="H13" t="n">
         <v>0.98712</v>
       </c>
       <c r="I13" t="n">
-        <v>0.24686</v>
+        <v>0.23796</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5992</v>
+        <v>0.6024799999999999</v>
       </c>
     </row>
     <row r="14">
@@ -982,10 +982,10 @@
         <v>0.6881999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1975999999999999</v>
+        <v>0.21404</v>
       </c>
       <c r="J14" t="n">
-        <v>0.64516</v>
+        <v>0.6303000000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1010,22 +1010,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.25468</v>
+        <v>0.27112</v>
       </c>
       <c r="F15" t="n">
-        <v>0.27076</v>
+        <v>0.28768</v>
       </c>
       <c r="G15" t="n">
-        <v>0.4656399999999999</v>
+        <v>0.47898</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7702800000000001</v>
+        <v>0.7712800000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1975999999999999</v>
+        <v>0.21404</v>
       </c>
       <c r="J15" t="n">
-        <v>0.64516</v>
+        <v>0.6303000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1050,22 +1050,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.89984</v>
+        <v>0.9014200000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9156000000000001</v>
+        <v>0.91676</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9243399999999999</v>
+        <v>0.9267</v>
       </c>
       <c r="H16" t="n">
         <v>0.9941600000000002</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1975999999999999</v>
+        <v>0.21404</v>
       </c>
       <c r="J16" t="n">
-        <v>0.64516</v>
+        <v>0.6303000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1090,22 +1090,22 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.04820000000000001</v>
+        <v>0.05300000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>0.04564</v>
+        <v>0.05078000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3333199999999999</v>
+        <v>0.3364200000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>0.68102</v>
+        <v>0.68408</v>
       </c>
       <c r="I17" t="n">
-        <v>0.22428</v>
+        <v>0.2365800000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6266</v>
+        <v>0.6118199999999999</v>
       </c>
     </row>
     <row r="18">
@@ -1130,22 +1130,22 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.27248</v>
+        <v>0.2895800000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2892400000000001</v>
+        <v>0.30206</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4759</v>
+        <v>0.4830599999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7764</v>
+        <v>0.7743599999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.22428</v>
+        <v>0.2365800000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6266</v>
+        <v>0.6118199999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1170,22 +1170,22 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.89908</v>
+        <v>0.9014</v>
       </c>
       <c r="F19" t="n">
-        <v>0.91088</v>
+        <v>0.9114800000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>0.92778</v>
+        <v>0.9312800000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9907</v>
+        <v>0.9883200000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>0.22428</v>
+        <v>0.2365800000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6266</v>
+        <v>0.6118199999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1210,22 +1210,22 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.06804</v>
+        <v>0.06874</v>
       </c>
       <c r="F20" t="n">
-        <v>0.07382</v>
+        <v>0.07486</v>
       </c>
       <c r="G20" t="n">
-        <v>0.36</v>
+        <v>0.36206</v>
       </c>
       <c r="H20" t="n">
-        <v>0.69336</v>
+        <v>0.6933400000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>0.23726</v>
+        <v>0.23314</v>
       </c>
       <c r="J20" t="n">
-        <v>0.58042</v>
+        <v>0.5869399999999999</v>
       </c>
     </row>
     <row r="21">
@@ -1250,22 +1250,22 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.3053</v>
+        <v>0.30188</v>
       </c>
       <c r="F21" t="n">
-        <v>0.32052</v>
+        <v>0.31438</v>
       </c>
       <c r="G21" t="n">
-        <v>0.50258</v>
+        <v>0.4902800000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>0.77742</v>
+        <v>0.7723199999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>0.23726</v>
+        <v>0.23314</v>
       </c>
       <c r="J21" t="n">
-        <v>0.58042</v>
+        <v>0.5869399999999999</v>
       </c>
     </row>
     <row r="22">
@@ -1290,22 +1290,22 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.8857200000000001</v>
+        <v>0.8888199999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>0.90084</v>
+        <v>0.9032</v>
       </c>
       <c r="G22" t="n">
-        <v>0.90784</v>
+        <v>0.91138</v>
       </c>
       <c r="H22" t="n">
         <v>0.98248</v>
       </c>
       <c r="I22" t="n">
-        <v>0.23726</v>
+        <v>0.23314</v>
       </c>
       <c r="J22" t="n">
-        <v>0.58042</v>
+        <v>0.5869399999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1330,10 +1330,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.04754</v>
+        <v>0.04958000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>0.04974</v>
+        <v>0.0518</v>
       </c>
       <c r="G23" t="n">
         <v>0.34358</v>
@@ -1342,10 +1342,10 @@
         <v>0.6851199999999998</v>
       </c>
       <c r="I23" t="n">
-        <v>0.20444</v>
+        <v>0.2112999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6471399999999999</v>
+        <v>0.63826</v>
       </c>
     </row>
     <row r="24">
@@ -1370,22 +1370,22 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.25198</v>
+        <v>0.2608799999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>0.26614</v>
+        <v>0.27386</v>
       </c>
       <c r="G24" t="n">
-        <v>0.46256</v>
+        <v>0.4718000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>0.76306</v>
+        <v>0.7579199999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>0.20444</v>
+        <v>0.2112999999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>0.6471399999999999</v>
+        <v>0.63826</v>
       </c>
     </row>
     <row r="25">
@@ -1410,22 +1410,22 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.8991199999999999</v>
+        <v>0.8991400000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>0.91792</v>
+        <v>0.9197200000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>0.92322</v>
+        <v>0.91974</v>
       </c>
       <c r="H25" t="n">
         <v>0.9941600000000002</v>
       </c>
       <c r="I25" t="n">
-        <v>0.20444</v>
+        <v>0.2112999999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>0.6471399999999999</v>
+        <v>0.63826</v>
       </c>
     </row>
     <row r="26">
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.05574000000000001</v>
+        <v>0.05914000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>0.05848</v>
+        <v>0.06258</v>
       </c>
       <c r="G26" t="n">
         <v>0.34666</v>
@@ -1462,10 +1462,10 @@
         <v>0.68308</v>
       </c>
       <c r="I26" t="n">
-        <v>0.25776</v>
+        <v>0.24138</v>
       </c>
       <c r="J26" t="n">
-        <v>0.5970399999999999</v>
+        <v>0.6061399999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1490,22 +1490,22 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.3135</v>
+        <v>0.30052</v>
       </c>
       <c r="F27" t="n">
-        <v>0.33334</v>
+        <v>0.31998</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5158800000000001</v>
+        <v>0.49436</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7795</v>
+        <v>0.7743599999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>0.25776</v>
+        <v>0.24138</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5970399999999999</v>
+        <v>0.6061399999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.9105399999999999</v>
+        <v>0.9066599999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>0.92644</v>
+        <v>0.9212199999999999</v>
       </c>
       <c r="G28" t="n">
         <v>0.9206999999999999</v>
@@ -1542,10 +1542,10 @@
         <v>0.98712</v>
       </c>
       <c r="I28" t="n">
-        <v>0.25776</v>
+        <v>0.24138</v>
       </c>
       <c r="J28" t="n">
-        <v>0.5970399999999999</v>
+        <v>0.6061399999999999</v>
       </c>
     </row>
     <row r="29">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.07896</v>
+        <v>0.08102000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>0.08819999999999999</v>
+        <v>0.09024</v>
       </c>
       <c r="G29" t="n">
         <v>0.37744</v>
@@ -1582,10 +1582,10 @@
         <v>0.7066800000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>0.20174</v>
+        <v>0.18598</v>
       </c>
       <c r="J29" t="n">
-        <v>0.6105400000000001</v>
+        <v>0.61028</v>
       </c>
     </row>
     <row r="30">
@@ -1610,22 +1610,22 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.2807</v>
+        <v>0.267</v>
       </c>
       <c r="F30" t="n">
-        <v>0.29436</v>
+        <v>0.2769200000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>0.49436</v>
+        <v>0.4851</v>
       </c>
       <c r="H30" t="n">
-        <v>0.77642</v>
+        <v>0.7640999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>0.20174</v>
+        <v>0.18598</v>
       </c>
       <c r="J30" t="n">
-        <v>0.6105400000000001</v>
+        <v>0.61028</v>
       </c>
     </row>
     <row r="31">
@@ -1650,22 +1650,22 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.89124</v>
+        <v>0.8772800000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>0.91028</v>
+        <v>0.89976</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9348000000000001</v>
+        <v>0.92666</v>
       </c>
       <c r="H31" t="n">
         <v>0.9836599999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>0.20174</v>
+        <v>0.18598</v>
       </c>
       <c r="J31" t="n">
-        <v>0.6105400000000001</v>
+        <v>0.61028</v>
       </c>
     </row>
     <row r="32">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.194172, "environmental": 0.131673, "comfort": 0.401912, "practicality": 0.272243}</t>
+          <t>{"energy_cost": 0.1943, "environmental": 0.131354, "comfort": 0.403745, "practicality": 0.2706}</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1702,10 +1702,10 @@
         <v>0.77434</v>
       </c>
       <c r="I32" t="n">
-        <v>0.09777999999999998</v>
+        <v>0.09576000000000001</v>
       </c>
       <c r="J32" t="n">
-        <v>0.59806</v>
+        <v>0.62416</v>
       </c>
     </row>
     <row r="33">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.194172, "environmental": 0.131673, "comfort": 0.401912, "practicality": 0.272243}</t>
+          <t>{"energy_cost": 0.1943, "environmental": 0.131354, "comfort": 0.403745, "practicality": 0.2706}</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1730,22 +1730,22 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.33128</v>
+        <v>0.32926</v>
       </c>
       <c r="F33" t="n">
-        <v>0.3527999999999999</v>
+        <v>0.35026</v>
       </c>
       <c r="G33" t="n">
-        <v>0.53538</v>
+        <v>0.5394599999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>0.8</v>
+        <v>0.79588</v>
       </c>
       <c r="I33" t="n">
-        <v>0.09777999999999998</v>
+        <v>0.09576000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>0.59806</v>
+        <v>0.62416</v>
       </c>
     </row>
     <row r="34">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.194172, "environmental": 0.131673, "comfort": 0.401912, "practicality": 0.272243}</t>
+          <t>{"energy_cost": 0.1943, "environmental": 0.131354, "comfort": 0.403745, "practicality": 0.2706}</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1770,22 +1770,22 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9293400000000001</v>
+        <v>0.95342</v>
       </c>
       <c r="F34" t="n">
-        <v>0.94702</v>
+        <v>0.96508</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9091800000000001</v>
+        <v>0.9406399999999999</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>0.09777999999999998</v>
+        <v>0.09576000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>0.59806</v>
+        <v>0.62416</v>
       </c>
     </row>
     <row r="35">
@@ -1822,10 +1822,10 @@
         <v>0.79078</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1661799999999999</v>
+        <v>0.15246</v>
       </c>
       <c r="J35" t="n">
-        <v>0.5196999999999999</v>
+        <v>0.5489599999999999</v>
       </c>
     </row>
     <row r="36">
@@ -1850,22 +1850,22 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.4407</v>
+        <v>0.42698</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4646199999999999</v>
+        <v>0.44924</v>
       </c>
       <c r="G36" t="n">
-        <v>0.61026</v>
+        <v>0.61128</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8359</v>
+        <v>0.8256399999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1661799999999999</v>
+        <v>0.15246</v>
       </c>
       <c r="J36" t="n">
-        <v>0.5196999999999999</v>
+        <v>0.5489599999999999</v>
       </c>
     </row>
     <row r="37">
@@ -1890,22 +1890,22 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.9603999999999999</v>
+        <v>0.9759399999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>0.97028</v>
+        <v>0.9819799999999999</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9464399999999999</v>
+        <v>0.9686</v>
       </c>
       <c r="H37" t="n">
         <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1661799999999999</v>
+        <v>0.15246</v>
       </c>
       <c r="J37" t="n">
-        <v>0.5196999999999999</v>
+        <v>0.5489599999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1942,10 +1942,10 @@
         <v>0.7640999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>0.07999999999999999</v>
+        <v>0.08068</v>
       </c>
       <c r="J38" t="n">
-        <v>0.6575</v>
+        <v>0.67626</v>
       </c>
     </row>
     <row r="39">
@@ -1970,22 +1970,22 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.2711</v>
+        <v>0.27178</v>
       </c>
       <c r="F39" t="n">
-        <v>0.28566</v>
+        <v>0.28664</v>
       </c>
       <c r="G39" t="n">
-        <v>0.48206</v>
+        <v>0.48308</v>
       </c>
       <c r="H39" t="n">
-        <v>0.7835799999999999</v>
+        <v>0.77744</v>
       </c>
       <c r="I39" t="n">
-        <v>0.07999999999999999</v>
+        <v>0.08068</v>
       </c>
       <c r="J39" t="n">
-        <v>0.6575</v>
+        <v>0.67626</v>
       </c>
     </row>
     <row r="40">
@@ -2010,22 +2010,22 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.9286</v>
+        <v>0.94804</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9458800000000001</v>
+        <v>0.961</v>
       </c>
       <c r="G40" t="n">
-        <v>0.92552</v>
+        <v>0.9313399999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>0.99886</v>
+        <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>0.07999999999999999</v>
+        <v>0.08068</v>
       </c>
       <c r="J40" t="n">
-        <v>0.6575</v>
+        <v>0.67626</v>
       </c>
     </row>
     <row r="41">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}</t>
+          <t>{"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2050,22 +2050,22 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.07146</v>
+        <v>0.07076</v>
       </c>
       <c r="F41" t="n">
         <v>0.08</v>
       </c>
       <c r="G41" t="n">
-        <v>0.37436</v>
+        <v>0.37538</v>
       </c>
       <c r="H41" t="n">
-        <v>0.69948</v>
+        <v>0.6974400000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1935</v>
+        <v>0.1798400000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>0.6169600000000001</v>
+        <v>0.6227799999999998</v>
       </c>
     </row>
     <row r="42">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}</t>
+          <t>{"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2090,22 +2090,22 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.26496</v>
+        <v>0.2506</v>
       </c>
       <c r="F42" t="n">
-        <v>0.2795</v>
+        <v>0.2646</v>
       </c>
       <c r="G42" t="n">
-        <v>0.48102</v>
+        <v>0.4800000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>0.76922</v>
+        <v>0.75898</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1935</v>
+        <v>0.1798400000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>0.6169600000000001</v>
+        <v>0.6227799999999998</v>
       </c>
     </row>
     <row r="43">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}</t>
+          <t>{"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2130,22 +2130,22 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.88192</v>
+        <v>0.8733799999999998</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9026799999999999</v>
+        <v>0.89628</v>
       </c>
       <c r="G43" t="n">
-        <v>0.9196</v>
+        <v>0.9137999999999999</v>
       </c>
       <c r="H43" t="n">
         <v>0.9836599999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>0.1935</v>
+        <v>0.1798400000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>0.6169600000000001</v>
+        <v>0.6227799999999998</v>
       </c>
     </row>
     <row r="44">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}}</t>
+          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}}</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2170,22 +2170,22 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.16168</v>
+        <v>0.16306</v>
       </c>
       <c r="F44" t="n">
-        <v>0.18358</v>
+        <v>0.18512</v>
       </c>
       <c r="G44" t="n">
-        <v>0.41434</v>
+        <v>0.41536</v>
       </c>
       <c r="H44" t="n">
-        <v>0.74154</v>
+        <v>0.74256</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2249800000000001</v>
+        <v>0.20856</v>
       </c>
       <c r="J44" t="n">
-        <v>0.5208999999999999</v>
+        <v>0.5281799999999999</v>
       </c>
     </row>
     <row r="45">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}}</t>
+          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}}</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2210,22 +2210,22 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.3866600000000001</v>
+        <v>0.37162</v>
       </c>
       <c r="F45" t="n">
-        <v>0.4097399999999999</v>
+        <v>0.39332</v>
       </c>
       <c r="G45" t="n">
-        <v>0.57128</v>
+        <v>0.57026</v>
       </c>
       <c r="H45" t="n">
-        <v>0.8348799999999998</v>
+        <v>0.8276999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>0.2249800000000001</v>
+        <v>0.20856</v>
       </c>
       <c r="J45" t="n">
-        <v>0.5208999999999999</v>
+        <v>0.5281799999999999</v>
       </c>
     </row>
     <row r="46">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}}</t>
+          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}}</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2250,22 +2250,22 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.9075599999999999</v>
+        <v>0.8997999999999999</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9219200000000001</v>
+        <v>0.91608</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9277599999999999</v>
+        <v>0.9231</v>
       </c>
       <c r="H46" t="n">
         <v>0.9836599999999999</v>
       </c>
       <c r="I46" t="n">
-        <v>0.2249800000000001</v>
+        <v>0.20856</v>
       </c>
       <c r="J46" t="n">
-        <v>0.5208999999999999</v>
+        <v>0.5281799999999999</v>
       </c>
     </row>
     <row r="47">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.268909, "environmental": 0.371359, "comfort": 0.160782, "practicality": 0.19895}</t>
+          <t>{"energy_cost": 0.268683, "environmental": 0.371046, "comfort": 0.16149, "practicality": 0.198782}</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2290,22 +2290,22 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.0393</v>
+        <v>0.03932</v>
       </c>
       <c r="F47" t="n">
-        <v>0.04102</v>
+        <v>0.04154</v>
       </c>
       <c r="G47" t="n">
-        <v>0.33846</v>
+        <v>0.33742</v>
       </c>
       <c r="H47" t="n">
-        <v>0.6707799999999999</v>
+        <v>0.67386</v>
       </c>
       <c r="I47" t="n">
-        <v>0.22908</v>
+        <v>0.2393200000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>0.6012000000000001</v>
+        <v>0.6018399999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.268909, "environmental": 0.371359, "comfort": 0.160782, "practicality": 0.19895}</t>
+          <t>{"energy_cost": 0.268683, "environmental": 0.371046, "comfort": 0.16149, "practicality": 0.198782}</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2330,22 +2330,22 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.26838</v>
+        <v>0.2786400000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>0.27948</v>
+        <v>0.28666</v>
       </c>
       <c r="G48" t="n">
-        <v>0.48</v>
+        <v>0.4851200000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>0.7702600000000001</v>
+        <v>0.7640800000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>0.22908</v>
+        <v>0.2393200000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>0.6012000000000001</v>
+        <v>0.6018399999999999</v>
       </c>
     </row>
     <row r="49">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.268909, "environmental": 0.371359, "comfort": 0.160782, "practicality": 0.19895}</t>
+          <t>{"energy_cost": 0.268683, "environmental": 0.371046, "comfort": 0.16149, "practicality": 0.198782}</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2370,22 +2370,22 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.86958</v>
+        <v>0.88048</v>
       </c>
       <c r="F49" t="n">
-        <v>0.8876200000000001</v>
+        <v>0.89578</v>
       </c>
       <c r="G49" t="n">
-        <v>0.90572</v>
+        <v>0.91738</v>
       </c>
       <c r="H49" t="n">
-        <v>0.9812999999999998</v>
+        <v>0.98598</v>
       </c>
       <c r="I49" t="n">
-        <v>0.22908</v>
+        <v>0.2393200000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>0.6012000000000001</v>
+        <v>0.6018399999999999</v>
       </c>
     </row>
     <row r="50">
@@ -2410,22 +2410,22 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.05572000000000001</v>
+        <v>0.05778000000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>0.05692000000000001</v>
+        <v>0.05898000000000001</v>
       </c>
       <c r="G50" t="n">
-        <v>0.34256</v>
+        <v>0.34668</v>
       </c>
       <c r="H50" t="n">
         <v>0.68206</v>
       </c>
       <c r="I50" t="n">
-        <v>0.25642</v>
+        <v>0.25982</v>
       </c>
       <c r="J50" t="n">
-        <v>0.5672999999999999</v>
+        <v>0.5641999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -2450,22 +2450,22 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.31214</v>
+        <v>0.3176</v>
       </c>
       <c r="F51" t="n">
-        <v>0.3318</v>
+        <v>0.33436</v>
       </c>
       <c r="G51" t="n">
-        <v>0.5117800000000001</v>
+        <v>0.5087200000000001</v>
       </c>
       <c r="H51" t="n">
-        <v>0.78768</v>
+        <v>0.78564</v>
       </c>
       <c r="I51" t="n">
-        <v>0.25642</v>
+        <v>0.25982</v>
       </c>
       <c r="J51" t="n">
-        <v>0.5672999999999999</v>
+        <v>0.5641999999999999</v>
       </c>
     </row>
     <row r="52">
@@ -2490,22 +2490,22 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.87944</v>
+        <v>0.8817999999999999</v>
       </c>
       <c r="F52" t="n">
-        <v>0.8985199999999999</v>
+        <v>0.8996600000000001</v>
       </c>
       <c r="G52" t="n">
-        <v>0.89394</v>
+        <v>0.8974399999999999</v>
       </c>
       <c r="H52" t="n">
         <v>0.98942</v>
       </c>
       <c r="I52" t="n">
-        <v>0.25642</v>
+        <v>0.25982</v>
       </c>
       <c r="J52" t="n">
-        <v>0.5672999999999999</v>
+        <v>0.5641999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -2530,22 +2530,22 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.004459999999999999</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F53" t="n">
-        <v>0.004119999999999999</v>
+        <v>0.006639999999999997</v>
       </c>
       <c r="G53" t="n">
-        <v>0.33024</v>
+        <v>0.33128</v>
       </c>
       <c r="H53" t="n">
-        <v>0.63486</v>
+        <v>0.63896</v>
       </c>
       <c r="I53" t="n">
-        <v>0.23658</v>
+        <v>0.24138</v>
       </c>
       <c r="J53" t="n">
-        <v>0.62146</v>
+        <v>0.6169600000000001</v>
       </c>
     </row>
     <row r="54">
@@ -2570,22 +2570,22 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.24104</v>
+        <v>0.24788</v>
       </c>
       <c r="F54" t="n">
-        <v>0.24974</v>
+        <v>0.25332</v>
       </c>
       <c r="G54" t="n">
-        <v>0.47074</v>
+        <v>0.47384</v>
       </c>
       <c r="H54" t="n">
-        <v>0.75588</v>
+        <v>0.75078</v>
       </c>
       <c r="I54" t="n">
-        <v>0.23658</v>
+        <v>0.24138</v>
       </c>
       <c r="J54" t="n">
-        <v>0.62146</v>
+        <v>0.6169600000000001</v>
       </c>
     </row>
     <row r="55">
@@ -2610,22 +2610,22 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.8625</v>
+        <v>0.8648400000000001</v>
       </c>
       <c r="F55" t="n">
-        <v>0.8793799999999999</v>
+        <v>0.8811199999999999</v>
       </c>
       <c r="G55" t="n">
-        <v>0.89276</v>
+        <v>0.89162</v>
       </c>
       <c r="H55" t="n">
-        <v>0.97898</v>
+        <v>0.9836599999999999</v>
       </c>
       <c r="I55" t="n">
-        <v>0.23658</v>
+        <v>0.24138</v>
       </c>
       <c r="J55" t="n">
-        <v>0.62146</v>
+        <v>0.6169600000000001</v>
       </c>
     </row>
     <row r="56">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}</t>
+          <t>{"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2650,22 +2650,22 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.05028000000000001</v>
+        <v>0.04684000000000001</v>
       </c>
       <c r="F56" t="n">
-        <v>0.05744</v>
+        <v>0.0523</v>
       </c>
       <c r="G56" t="n">
-        <v>0.34154</v>
+        <v>0.3374199999999999</v>
       </c>
       <c r="H56" t="n">
-        <v>0.6677</v>
+        <v>0.66874</v>
       </c>
       <c r="I56" t="n">
-        <v>0.2304</v>
+        <v>0.24272</v>
       </c>
       <c r="J56" t="n">
-        <v>0.5647</v>
+        <v>0.5698399999999999</v>
       </c>
     </row>
     <row r="57">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}</t>
+          <t>{"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2690,22 +2690,22 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.28068</v>
+        <v>0.28956</v>
       </c>
       <c r="F57" t="n">
-        <v>0.29744</v>
+        <v>0.30204</v>
       </c>
       <c r="G57" t="n">
-        <v>0.4851200000000001</v>
+        <v>0.49024</v>
       </c>
       <c r="H57" t="n">
-        <v>0.7712600000000001</v>
+        <v>0.76514</v>
       </c>
       <c r="I57" t="n">
-        <v>0.2304</v>
+        <v>0.24272</v>
       </c>
       <c r="J57" t="n">
-        <v>0.5647</v>
+        <v>0.5698399999999999</v>
       </c>
     </row>
     <row r="58">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}</t>
+          <t>{"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2730,22 +2730,22 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.8453799999999999</v>
+        <v>0.8593999999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>0.8689</v>
+        <v>0.8788199999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>0.8648199999999999</v>
+        <v>0.8823399999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>0.98016</v>
+        <v>0.9836599999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>0.2304</v>
+        <v>0.24272</v>
       </c>
       <c r="J58" t="n">
-        <v>0.5647</v>
+        <v>0.5698399999999999</v>
       </c>
     </row>
     <row r="59">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}}</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2770,22 +2770,22 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.03932</v>
+        <v>0.04274</v>
       </c>
       <c r="F59" t="n">
-        <v>0.0364</v>
+        <v>0.03948</v>
       </c>
       <c r="G59" t="n">
-        <v>0.34562</v>
+        <v>0.3477</v>
       </c>
       <c r="H59" t="n">
-        <v>0.67284</v>
+        <v>0.6769400000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>0.23452</v>
+        <v>0.2393</v>
       </c>
       <c r="J59" t="n">
-        <v>0.6103799999999999</v>
+        <v>0.60608</v>
       </c>
     </row>
     <row r="60">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}}</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2810,22 +2810,22 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.27384</v>
+        <v>0.28204</v>
       </c>
       <c r="F60" t="n">
-        <v>0.28566</v>
+        <v>0.29128</v>
       </c>
       <c r="G60" t="n">
-        <v>0.49024</v>
+        <v>0.4964200000000001</v>
       </c>
       <c r="H60" t="n">
-        <v>0.77846</v>
+        <v>0.77128</v>
       </c>
       <c r="I60" t="n">
-        <v>0.23452</v>
+        <v>0.2393</v>
       </c>
       <c r="J60" t="n">
-        <v>0.6103799999999999</v>
+        <v>0.60608</v>
       </c>
     </row>
     <row r="61">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}}</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2850,22 +2850,22 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.88422</v>
+        <v>0.88812</v>
       </c>
       <c r="F61" t="n">
-        <v>0.9009</v>
+        <v>0.90388</v>
       </c>
       <c r="G61" t="n">
-        <v>0.93008</v>
+        <v>0.9313</v>
       </c>
       <c r="H61" t="n">
-        <v>0.9859599999999998</v>
+        <v>0.9906599999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>0.23452</v>
+        <v>0.2393</v>
       </c>
       <c r="J61" t="n">
-        <v>0.6103799999999999</v>
+        <v>0.60608</v>
       </c>
     </row>
     <row r="62">
@@ -2902,10 +2902,10 @@
         <v>0.67798</v>
       </c>
       <c r="I62" t="n">
-        <v>0.29336</v>
+        <v>0.29542</v>
       </c>
       <c r="J62" t="n">
-        <v>0.5467200000000001</v>
+        <v>0.54542</v>
       </c>
     </row>
     <row r="63">
@@ -2930,22 +2930,22 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.36548</v>
+        <v>0.36754</v>
       </c>
       <c r="F63" t="n">
-        <v>0.3845999999999999</v>
+        <v>0.38564</v>
       </c>
       <c r="G63" t="n">
-        <v>0.5518000000000001</v>
+        <v>0.5456199999999999</v>
       </c>
       <c r="H63" t="n">
-        <v>0.8194799999999999</v>
+        <v>0.8154</v>
       </c>
       <c r="I63" t="n">
-        <v>0.29336</v>
+        <v>0.29542</v>
       </c>
       <c r="J63" t="n">
-        <v>0.5467200000000001</v>
+        <v>0.54542</v>
       </c>
     </row>
     <row r="64">
@@ -2970,22 +2970,22 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.9122</v>
+        <v>0.91296</v>
       </c>
       <c r="F64" t="n">
-        <v>0.9224399999999999</v>
+        <v>0.92302</v>
       </c>
       <c r="G64" t="n">
-        <v>0.93244</v>
+        <v>0.9335800000000001</v>
       </c>
       <c r="H64" t="n">
         <v>0.9812799999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>0.29336</v>
+        <v>0.29542</v>
       </c>
       <c r="J64" t="n">
-        <v>0.5467200000000001</v>
+        <v>0.54542</v>
       </c>
     </row>
     <row r="65">
@@ -3022,10 +3022,10 @@
         <v>0.6882200000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>0.25368</v>
+        <v>0.25574</v>
       </c>
       <c r="J65" t="n">
-        <v>0.5893999999999999</v>
+        <v>0.5881000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -3050,22 +3050,22 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.31966</v>
+        <v>0.32172</v>
       </c>
       <c r="F66" t="n">
-        <v>0.34616</v>
+        <v>0.34718</v>
       </c>
       <c r="G66" t="n">
-        <v>0.51384</v>
+        <v>0.5076799999999999</v>
       </c>
       <c r="H66" t="n">
-        <v>0.8</v>
+        <v>0.7959000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>0.25368</v>
+        <v>0.25574</v>
       </c>
       <c r="J66" t="n">
-        <v>0.5893999999999999</v>
+        <v>0.5881000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -3090,22 +3090,22 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.90906</v>
+        <v>0.9098200000000001</v>
       </c>
       <c r="F67" t="n">
-        <v>0.92012</v>
+        <v>0.9206800000000002</v>
       </c>
       <c r="G67" t="n">
-        <v>0.92078</v>
+        <v>0.9219200000000001</v>
       </c>
       <c r="H67" t="n">
         <v>0.9812799999999999</v>
       </c>
       <c r="I67" t="n">
-        <v>0.25368</v>
+        <v>0.25574</v>
       </c>
       <c r="J67" t="n">
-        <v>0.5893999999999999</v>
+        <v>0.5881000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -3142,10 +3142,10 @@
         <v>0.70974</v>
       </c>
       <c r="I68" t="n">
-        <v>0.13058</v>
+        <v>0.1142</v>
       </c>
       <c r="J68" t="n">
-        <v>0.6389999999999998</v>
+        <v>0.6468400000000001</v>
       </c>
     </row>
     <row r="69">
@@ -3170,22 +3170,22 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.24374</v>
+        <v>0.22736</v>
       </c>
       <c r="F69" t="n">
-        <v>0.26052</v>
+        <v>0.24254</v>
       </c>
       <c r="G69" t="n">
-        <v>0.46872</v>
+        <v>0.4615600000000001</v>
       </c>
       <c r="H69" t="n">
-        <v>0.7558999999999999</v>
+        <v>0.7507600000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>0.13058</v>
+        <v>0.1142</v>
       </c>
       <c r="J69" t="n">
-        <v>0.6389999999999998</v>
+        <v>0.6468400000000001</v>
       </c>
     </row>
     <row r="70">
@@ -3210,22 +3210,22 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.8827399999999999</v>
+        <v>0.8742000000000001</v>
       </c>
       <c r="F70" t="n">
-        <v>0.9026999999999999</v>
+        <v>0.89688</v>
       </c>
       <c r="G70" t="n">
-        <v>0.91264</v>
+        <v>0.90564</v>
       </c>
       <c r="H70" t="n">
         <v>0.9836599999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>0.13058</v>
+        <v>0.1142</v>
       </c>
       <c r="J70" t="n">
-        <v>0.6389999999999998</v>
+        <v>0.6468400000000001</v>
       </c>
     </row>
     <row r="71">
@@ -3250,22 +3250,22 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.04072</v>
+        <v>0.04274</v>
       </c>
       <c r="F71" t="n">
-        <v>0.03793999999999999</v>
+        <v>0.04049999999999999</v>
       </c>
       <c r="G71" t="n">
-        <v>0.34562</v>
+        <v>0.34668</v>
       </c>
       <c r="H71" t="n">
-        <v>0.6748800000000001</v>
+        <v>0.679</v>
       </c>
       <c r="I71" t="n">
-        <v>0.23176</v>
+        <v>0.23726</v>
       </c>
       <c r="J71" t="n">
-        <v>0.6125</v>
+        <v>0.605</v>
       </c>
     </row>
     <row r="72">
@@ -3290,22 +3290,22 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.27248</v>
+        <v>0.28</v>
       </c>
       <c r="F72" t="n">
-        <v>0.28462</v>
+        <v>0.28974</v>
       </c>
       <c r="G72" t="n">
-        <v>0.4892</v>
+        <v>0.49332</v>
       </c>
       <c r="H72" t="n">
-        <v>0.77846</v>
+        <v>0.77128</v>
       </c>
       <c r="I72" t="n">
-        <v>0.23176</v>
+        <v>0.23726</v>
       </c>
       <c r="J72" t="n">
-        <v>0.6125</v>
+        <v>0.605</v>
       </c>
     </row>
     <row r="73">
@@ -3330,22 +3330,22 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.88498</v>
+        <v>0.885</v>
       </c>
       <c r="F73" t="n">
-        <v>0.90266</v>
+        <v>0.9026799999999999</v>
       </c>
       <c r="G73" t="n">
-        <v>0.9289400000000001</v>
+        <v>0.92432</v>
       </c>
       <c r="H73" t="n">
-        <v>0.9882799999999999</v>
+        <v>0.9929600000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>0.23176</v>
+        <v>0.23726</v>
       </c>
       <c r="J73" t="n">
-        <v>0.6125</v>
+        <v>0.605</v>
       </c>
     </row>
   </sheetData>

--- a/Output Files GPT-OSS 20B/sensitivity_analysis_gptoss.xlsx
+++ b/Output Files GPT-OSS 20B/sensitivity_analysis_gptoss.xlsx
@@ -3121,7 +3121,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.248, "environmental": 0.244, "comfort": 0.203, "practicality": 0.305}}</t>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.251251, "environmental": 0.245245, "comfort": 0.203203, "practicality": 0.3003}}</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -3130,22 +3130,22 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.11316</v>
+        <v>0.10632</v>
       </c>
       <c r="F68" t="n">
-        <v>0.11998</v>
+        <v>0.11384</v>
       </c>
       <c r="G68" t="n">
-        <v>0.39076</v>
+        <v>0.38256</v>
       </c>
       <c r="H68" t="n">
-        <v>0.70974</v>
+        <v>0.7056600000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>0.1142</v>
+        <v>0.12104</v>
       </c>
       <c r="J68" t="n">
-        <v>0.6468400000000001</v>
+        <v>0.6445200000000002</v>
       </c>
     </row>
     <row r="69">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.248, "environmental": 0.244, "comfort": 0.203, "practicality": 0.305}}</t>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.251251, "environmental": 0.245245, "comfort": 0.203203, "practicality": 0.3003}}</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3173,19 +3173,19 @@
         <v>0.22736</v>
       </c>
       <c r="F69" t="n">
-        <v>0.24254</v>
+        <v>0.24204</v>
       </c>
       <c r="G69" t="n">
-        <v>0.4615600000000001</v>
+        <v>0.46462</v>
       </c>
       <c r="H69" t="n">
-        <v>0.7507600000000001</v>
+        <v>0.74664</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1142</v>
+        <v>0.12104</v>
       </c>
       <c r="J69" t="n">
-        <v>0.6468400000000001</v>
+        <v>0.6445200000000002</v>
       </c>
     </row>
     <row r="70">
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.248, "environmental": 0.244, "comfort": 0.203, "practicality": 0.305}}</t>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.251251, "environmental": 0.245245, "comfort": 0.203203, "practicality": 0.3003}}</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3210,22 +3210,22 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.8742000000000001</v>
+        <v>0.8718800000000002</v>
       </c>
       <c r="F70" t="n">
-        <v>0.89688</v>
+        <v>0.8951399999999999</v>
       </c>
       <c r="G70" t="n">
-        <v>0.90564</v>
+        <v>0.9021399999999999</v>
       </c>
       <c r="H70" t="n">
         <v>0.9836599999999999</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1142</v>
+        <v>0.12104</v>
       </c>
       <c r="J70" t="n">
-        <v>0.6468400000000001</v>
+        <v>0.6445200000000002</v>
       </c>
     </row>
     <row r="71">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.333666, "environmental": 0.313686, "comfort": 0.126873, "practicality": 0.225774}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.335, "environmental": 0.316, "comfort": 0.122, "practicality": 0.227}}</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3253,19 +3253,19 @@
         <v>0.04274</v>
       </c>
       <c r="F71" t="n">
-        <v>0.04049999999999999</v>
+        <v>0.03948</v>
       </c>
       <c r="G71" t="n">
-        <v>0.34668</v>
+        <v>0.3477</v>
       </c>
       <c r="H71" t="n">
-        <v>0.679</v>
+        <v>0.6769400000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>0.23726</v>
+        <v>0.2393</v>
       </c>
       <c r="J71" t="n">
-        <v>0.605</v>
+        <v>0.60608</v>
       </c>
     </row>
     <row r="72">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.333666, "environmental": 0.313686, "comfort": 0.126873, "practicality": 0.225774}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.335, "environmental": 0.316, "comfort": 0.122, "practicality": 0.227}}</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3290,22 +3290,22 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.28</v>
+        <v>0.28204</v>
       </c>
       <c r="F72" t="n">
-        <v>0.28974</v>
+        <v>0.29128</v>
       </c>
       <c r="G72" t="n">
-        <v>0.49332</v>
+        <v>0.4964200000000001</v>
       </c>
       <c r="H72" t="n">
         <v>0.77128</v>
       </c>
       <c r="I72" t="n">
-        <v>0.23726</v>
+        <v>0.2393</v>
       </c>
       <c r="J72" t="n">
-        <v>0.605</v>
+        <v>0.60608</v>
       </c>
     </row>
     <row r="73">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.333666, "environmental": 0.313686, "comfort": 0.126873, "practicality": 0.225774}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.335, "environmental": 0.316, "comfort": 0.122, "practicality": 0.227}}</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3330,22 +3330,22 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.885</v>
+        <v>0.88812</v>
       </c>
       <c r="F73" t="n">
-        <v>0.9026799999999999</v>
+        <v>0.90388</v>
       </c>
       <c r="G73" t="n">
-        <v>0.92432</v>
+        <v>0.9313</v>
       </c>
       <c r="H73" t="n">
-        <v>0.9929600000000001</v>
+        <v>0.9906599999999999</v>
       </c>
       <c r="I73" t="n">
-        <v>0.23726</v>
+        <v>0.2393</v>
       </c>
       <c r="J73" t="n">
-        <v>0.605</v>
+        <v>0.60608</v>
       </c>
     </row>
   </sheetData>
